--- a/datasets/mp/05 Comentarios de clientas - sintético.xlsx
+++ b/datasets/mp/05 Comentarios de clientas - sintético.xlsx
@@ -2553,7 +2553,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATOS 100 % FICTICIOS para el programa IA-abilities (Coknow). Marcas, referencias, zonas, códigos de asesora, cifras y comentarios son inventados. No corresponden a la Compañía ni a ninguna empresa o persona real.</t>
+          <t>DATOS 100 % FICTICIOS para el programa IA-abilities. Marcas, referencias, zonas, códigos de asesora, cifras y comentarios son inventados. No corresponden a la Compañía ni a ninguna empresa o persona real.</t>
         </is>
       </c>
     </row>

--- a/datasets/mp/05 Comentarios de clientas - sintético.xlsx
+++ b/datasets/mp/05 Comentarios de clientas - sintético.xlsx
@@ -501,7 +501,6 @@
           <t>General</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>El cambio de talla fue rápido esta vez, mejoraron mucho.</t>
@@ -884,7 +883,6 @@
           <t>Hogar</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>La vajilla llegó con dos platos partidos. El empaque es muy débil para algo así.</t>
@@ -917,7 +915,6 @@
           <t>General</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>El pedido llegó completo y bien empacado. Gracias.</t>
@@ -950,7 +947,6 @@
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Los aretes de acero no me dieron alergia, por fin unos que puedo usar.</t>
@@ -1018,7 +1014,6 @@
           <t>Calzado</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Las botas cortas me sacaron ampolla el primer día, y a mi hermana también. Algo pasa con la horma.</t>
@@ -1086,7 +1081,6 @@
           <t>Lencería</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Muy buen precio en las fajas pero la tabla de tallas no sirve.</t>
@@ -1119,7 +1113,6 @@
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>El bolso tote es precioso y súper práctico.</t>
@@ -1152,7 +1145,6 @@
           <t>Belleza</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>El kit de uñas está muy completo para lo que cuesta.</t>
@@ -1220,7 +1212,6 @@
           <t>Hogar</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>El set de ollas es una maravilla, se nota la calidad.</t>
@@ -1288,7 +1279,6 @@
           <t>Belleza</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>La loción para hombre se la regalé a mi esposo y le encantó.</t>
@@ -1566,7 +1556,6 @@
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>La correa de cuero se ve finísima, perfecta para regalo.</t>
@@ -1599,7 +1588,6 @@
           <t>Ropa exterior</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Excelente el catálogo de este mes, muy bonitas las fotos y fácil de mostrar a las clientas.</t>
@@ -1702,7 +1690,6 @@
           <t>Ropa exterior</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>El jean tiro alto horma perfecto, mis clientas lo están pidiendo otra vez.</t>
@@ -1770,7 +1757,6 @@
           <t>General</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>¿Por qué ya no sacan la línea de hombre en tallas grandes?</t>
@@ -1803,7 +1789,6 @@
           <t>Lencería</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>La bata satinada es divina, la tela se siente de buena calidad y llegó a tiempo.</t>
@@ -1906,7 +1891,6 @@
           <t>Lencería</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Pedí la faja en talla M como siempre y me quedó pequeñísima, toca devolverla y el trámite es eterno.</t>
@@ -1939,7 +1923,6 @@
           <t>Belleza</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>El perfume dama huele delicioso y dura todo el día. Mis clientas lo aman.</t>
@@ -1972,7 +1955,6 @@
           <t>Calzado</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Los tenis del niño le duraron todo el semestre, muy buenos.</t>
@@ -2250,7 +2232,6 @@
           <t>Lencería</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>El brasier sin varilla es lo más cómodo que he tenido, ya voy por el tercero.</t>
@@ -2318,7 +2299,6 @@
           <t>Ropa exterior</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>La chaqueta denim llegó sin un botón. La asesora me ayudó con el cambio pero me demoró dos semanas.</t>
@@ -2491,7 +2471,6 @@
           <t>Accesorios</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>El morral escolar aguantó todo el año, muy resistente.</t>
@@ -2592,20 +2571,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sembrados: hay sarcasmo («Qué maravilla esperar tres semanas…», «Excelente servicio… si uno tiene paciencia…»), comentarios sin calificación,</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>y un patrón que coincide con el archivo 01 (la bota corta tiene problema de horma). Bueno para cruzar dos archivos.</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
